--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Person.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Person.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">narrator</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.352</t>
+    <t xml:space="preserve">EA 23.355</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
